--- a/StructureDefinition-legemiddel-classification.xlsx
+++ b/StructureDefinition-legemiddel-classification.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-legemiddel-classification.xlsx
+++ b/StructureDefinition-legemiddel-classification.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-legemiddel-classification.xlsx
+++ b/StructureDefinition-legemiddel-classification.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-legemiddel-classification.xlsx
+++ b/StructureDefinition-legemiddel-classification.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-legemiddel-classification.xlsx
+++ b/StructureDefinition-legemiddel-classification.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
